--- a/countries/is/2026-2029.xlsx
+++ b/countries/is/2026-2029.xlsx
@@ -32311,16 +32311,16 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O217" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P217" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R217" t="n">
-        <v>4.722503224972597</v>
+        <v>4.971056026286944</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -32680,6 +32680,741 @@
         </is>
       </c>
       <c r="BC219" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>12</v>
+      </c>
+      <c r="O220" t="n">
+        <v>12</v>
+      </c>
+      <c r="P220" t="n">
+        <v>12</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.982633615772166</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_COVID19_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_COVID19_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_PERTUSSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_PERTUSSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>22</v>
+      </c>
+      <c r="O222" t="n">
+        <v>22</v>
+      </c>
+      <c r="P222" t="n">
+        <v>22</v>
+      </c>
+      <c r="R222" t="n">
+        <v>5.468161628915639</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_INFLUENZA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_INFLUENZA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_MYCO_PNEUMONIA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_RSV_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_RESPIRATORY_RSV_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
@@ -32718,7 +33453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -32801,7 +33536,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -32811,7 +33546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -32863,7 +33598,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2319</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="16">
